--- a/app/src/main/assets/methodmesh/odk_templates/tamagotchi/example_odk_tamagotchi_teaching.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/tamagotchi/example_odk_tamagotchi_teaching.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rb7f592eeff15465e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rcff32936d28944b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R03d0571c05174f10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rff091389c7a24009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R06c1732595e74616"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rd13bbe07ecc14c26"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1449,8 +1449,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="50" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1458,32 +1460,36 @@
         <x:v>form_title</x:v>
       </x:c>
       <x:c r="B1" s="7" t="str">
-        <x:v>MethodMesh Tamagotchi Teaching Journey</x:v>
+        <x:v>form_id</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>instance_name</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>form_id</x:v>
+        <x:v>MethodMesh Tamagotchi Teaching Journey</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
         <x:v>methodmesh_tamagotchi_teaching_v01</x:v>
       </x:c>
+      <x:c r="C2" t="str">
+        <x:v>2026092201</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Tamagotchi ${tamagotchi_session_id}</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="11" t="str">
-        <x:v>version</x:v>
-      </x:c>
-      <x:c r="B3" s="7" t="str">
-        <x:v>2026090801</x:v>
-      </x:c>
+      <x:c r="A3" s="11"/>
+      <x:c r="B3" s="7"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11" t="str">
-        <x:v>instance_name</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="str">
-        <x:v>Tamagotchi ${tamagotchi_session_id}</x:v>
-      </x:c>
+      <x:c r="A4" s="11"/>
+      <x:c r="B4" s="7"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
